--- a/VerveStacks_IND_grids_kan10/SysSettings.xlsx
+++ b/VerveStacks_IND_grids_kan10/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39538AE7-0674-43E4-97B0-5AC7B6E41D2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FE754BB-D272-42A0-88D7-4A1140300A3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="2340" windowWidth="28935" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -1791,199 +1791,199 @@
     <t>~fi_comm</t>
   </si>
   <si>
-    <t>e_IN684-765_IND</t>
+    <t>e_Bhuj_IND</t>
+  </si>
+  <si>
+    <t>grid node -- way/688672711-765 (Bhuj, 24 km)</t>
+  </si>
+  <si>
+    <t>lo</t>
+  </si>
+  <si>
+    <t>e_Dharmapuri_IND</t>
+  </si>
+  <si>
+    <t>grid node -- way/386153973-765 (Dharmapuri, 14 km)</t>
+  </si>
+  <si>
+    <t>e_Fatehpur_IND</t>
+  </si>
+  <si>
+    <t>grid node -- way/311118424-765 (Fatehpur, 6 km)</t>
+  </si>
+  <si>
+    <t>e_Indore_IND</t>
+  </si>
+  <si>
+    <t>grid node -- way/209826798-765 (Indore, 22 km)</t>
+  </si>
+  <si>
+    <t>e_Jaipur_IND</t>
+  </si>
+  <si>
+    <t>grid node -- way/369866141-765 (Jaipur, 31 km)</t>
+  </si>
+  <si>
+    <t>e_Korba_IND</t>
+  </si>
+  <si>
+    <t>grid node -- way/353914865-765 (Kolga, 12 km)</t>
+  </si>
+  <si>
+    <t>e_Kurnool_IND</t>
+  </si>
+  <si>
+    <t>grid node -- way/315823978-765 (Kurnool, 22 km)</t>
+  </si>
+  <si>
+    <t>e_Medinipur_IND</t>
+  </si>
+  <si>
+    <t>grid node -- way/759521252-765 (Kharagpur, 41 km)</t>
+  </si>
+  <si>
+    <t>e_Moga_IND</t>
+  </si>
+  <si>
+    <t>grid node -- way/372701897-765 (Moga, 5 km)</t>
+  </si>
+  <si>
+    <t>e_Phalodi_IND</t>
+  </si>
+  <si>
+    <t>grid node -- way/1143180503-765 (Phalodi, 44 km)</t>
+  </si>
+  <si>
+    <t>e_Rajahmundry_IND</t>
   </si>
   <si>
     <t>grid node -- IN684-765 (Kakinada, 44 km)</t>
   </si>
   <si>
-    <t>lo</t>
-  </si>
-  <si>
-    <t>e_w1143180503-765_IND</t>
-  </si>
-  <si>
-    <t>grid node -- way/1143180503-765 (Phalodi, 44 km)</t>
-  </si>
-  <si>
-    <t>e_w201845280-765_IND</t>
+    <t>e_Sikandarabad_IND</t>
+  </si>
+  <si>
+    <t>grid node -- way/420797421-765 (Faridabad, 46 km)</t>
+  </si>
+  <si>
+    <t>e_Solapur_IND</t>
+  </si>
+  <si>
+    <t>grid node -- way/293597835-765 (Solapur, 16 km)</t>
+  </si>
+  <si>
+    <t>e_Tezpur_IND</t>
+  </si>
+  <si>
+    <t>grid node -- way/203673991-400 (Tezpur, 27 km)</t>
+  </si>
+  <si>
+    <t>e_Vadodara_IND</t>
+  </si>
+  <si>
+    <t>grid node -- way/331275940-765 (Vadodara, 18 km)</t>
+  </si>
+  <si>
+    <t>e_Wardha_IND</t>
   </si>
   <si>
     <t>grid node -- way/201845280-765 (Wardha, 14 km)</t>
   </si>
   <si>
-    <t>e_w203673991-400_IND</t>
-  </si>
-  <si>
-    <t>grid node -- way/203673991-400 (Tezpur, 27 km)</t>
-  </si>
-  <si>
-    <t>e_w209826798-765_IND</t>
-  </si>
-  <si>
-    <t>grid node -- way/209826798-765 (Indore, 22 km)</t>
-  </si>
-  <si>
-    <t>e_w293597835-765_IND</t>
-  </si>
-  <si>
-    <t>grid node -- way/293597835-765 (Solapur, 16 km)</t>
-  </si>
-  <si>
-    <t>e_w311118424-765_IND</t>
-  </si>
-  <si>
-    <t>grid node -- way/311118424-765 (Fatehpur, 6 km)</t>
-  </si>
-  <si>
-    <t>e_w315823978-765_IND</t>
-  </si>
-  <si>
-    <t>grid node -- way/315823978-765 (Kurnool, 22 km)</t>
-  </si>
-  <si>
-    <t>e_w331275940-765_IND</t>
-  </si>
-  <si>
-    <t>grid node -- way/331275940-765 (Vadodara, 18 km)</t>
-  </si>
-  <si>
-    <t>e_w353914865-765_IND</t>
-  </si>
-  <si>
-    <t>grid node -- way/353914865-765 (Kolga, 12 km)</t>
-  </si>
-  <si>
-    <t>e_w369866141-765_IND</t>
-  </si>
-  <si>
-    <t>grid node -- way/369866141-765 (Jaipur, 31 km)</t>
-  </si>
-  <si>
-    <t>e_w372701897-765_IND</t>
-  </si>
-  <si>
-    <t>grid node -- way/372701897-765 (Moga, 5 km)</t>
-  </si>
-  <si>
-    <t>e_w386153973-765_IND</t>
-  </si>
-  <si>
-    <t>grid node -- way/386153973-765 (Dharmapuri, 14 km)</t>
-  </si>
-  <si>
-    <t>e_w420797421-765_IND</t>
-  </si>
-  <si>
-    <t>grid node -- way/420797421-765 (Faridabad, 46 km)</t>
-  </si>
-  <si>
-    <t>e_w688672711-765_IND</t>
-  </si>
-  <si>
-    <t>grid node -- way/688672711-765 (Bhuj, 24 km)</t>
-  </si>
-  <si>
-    <t>e_w759521252-765_IND</t>
-  </si>
-  <si>
-    <t>grid node -- way/759521252-765 (Kharagpur, 41 km)</t>
-  </si>
-  <si>
-    <t>h_IN684-765_IND</t>
+    <t>h_Bhuj_IND</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/688672711-765 (Bhuj, 24 km)</t>
+  </si>
+  <si>
+    <t>h_Dharmapuri_IND</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/386153973-765 (Dharmapuri, 14 km)</t>
+  </si>
+  <si>
+    <t>h_Fatehpur_IND</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/311118424-765 (Fatehpur, 6 km)</t>
+  </si>
+  <si>
+    <t>h_Indore_IND</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/209826798-765 (Indore, 22 km)</t>
+  </si>
+  <si>
+    <t>h_Jaipur_IND</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/369866141-765 (Jaipur, 31 km)</t>
+  </si>
+  <si>
+    <t>h_Korba_IND</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/353914865-765 (Kolga, 12 km)</t>
+  </si>
+  <si>
+    <t>h_Kurnool_IND</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/315823978-765 (Kurnool, 22 km)</t>
+  </si>
+  <si>
+    <t>h_Medinipur_IND</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/759521252-765 (Kharagpur, 41 km)</t>
+  </si>
+  <si>
+    <t>h_Moga_IND</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/372701897-765 (Moga, 5 km)</t>
+  </si>
+  <si>
+    <t>h_Phalodi_IND</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/1143180503-765 (Phalodi, 44 km)</t>
+  </si>
+  <si>
+    <t>h_Rajahmundry_IND</t>
   </si>
   <si>
     <t>heat at grid node -- IN684-765 (Kakinada, 44 km)</t>
   </si>
   <si>
-    <t>h_w1143180503-765_IND</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/1143180503-765 (Phalodi, 44 km)</t>
-  </si>
-  <si>
-    <t>h_w201845280-765_IND</t>
+    <t>h_Sikandarabad_IND</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/420797421-765 (Faridabad, 46 km)</t>
+  </si>
+  <si>
+    <t>h_Solapur_IND</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/293597835-765 (Solapur, 16 km)</t>
+  </si>
+  <si>
+    <t>h_Tezpur_IND</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/203673991-400 (Tezpur, 27 km)</t>
+  </si>
+  <si>
+    <t>h_Vadodara_IND</t>
+  </si>
+  <si>
+    <t>heat at grid node -- way/331275940-765 (Vadodara, 18 km)</t>
+  </si>
+  <si>
+    <t>h_Wardha_IND</t>
   </si>
   <si>
     <t>heat at grid node -- way/201845280-765 (Wardha, 14 km)</t>
-  </si>
-  <si>
-    <t>h_w203673991-400_IND</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/203673991-400 (Tezpur, 27 km)</t>
-  </si>
-  <si>
-    <t>h_w209826798-765_IND</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/209826798-765 (Indore, 22 km)</t>
-  </si>
-  <si>
-    <t>h_w293597835-765_IND</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/293597835-765 (Solapur, 16 km)</t>
-  </si>
-  <si>
-    <t>h_w311118424-765_IND</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/311118424-765 (Fatehpur, 6 km)</t>
-  </si>
-  <si>
-    <t>h_w315823978-765_IND</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/315823978-765 (Kurnool, 22 km)</t>
-  </si>
-  <si>
-    <t>h_w331275940-765_IND</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/331275940-765 (Vadodara, 18 km)</t>
-  </si>
-  <si>
-    <t>h_w353914865-765_IND</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/353914865-765 (Kolga, 12 km)</t>
-  </si>
-  <si>
-    <t>h_w369866141-765_IND</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/369866141-765 (Jaipur, 31 km)</t>
-  </si>
-  <si>
-    <t>h_w372701897-765_IND</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/372701897-765 (Moga, 5 km)</t>
-  </si>
-  <si>
-    <t>h_w386153973-765_IND</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/386153973-765 (Dharmapuri, 14 km)</t>
-  </si>
-  <si>
-    <t>h_w420797421-765_IND</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/420797421-765 (Faridabad, 46 km)</t>
-  </si>
-  <si>
-    <t>h_w688672711-765_IND</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/688672711-765 (Bhuj, 24 km)</t>
-  </si>
-  <si>
-    <t>h_w759521252-765_IND</t>
-  </si>
-  <si>
-    <t>heat at grid node -- way/759521252-765 (Kharagpur, 41 km)</t>
   </si>
 </sst>
 </file>
@@ -4398,7 +4398,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54078034-B753-4DE2-A6FF-130E5B1AFBAB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16D456FC-24B3-4CB5-9753-241A2423764F}">
   <dimension ref="B3:I20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -4855,7 +4855,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2622754F-99B7-49EE-AD66-B7688088B02F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D9599A1-DD50-435D-BF2E-C3A4946395B4}">
   <dimension ref="B3:I20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>

--- a/VerveStacks_IND_grids_kan10/SysSettings.xlsx
+++ b/VerveStacks_IND_grids_kan10/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FE754BB-D272-42A0-88D7-4A1140300A3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C913182-F64E-49ED-81A4-F8F0C953F6A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2340" windowWidth="28935" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2061" uniqueCount="648">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2063" uniqueCount="650">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -1984,6 +1984,12 @@
   </si>
   <si>
     <t>heat at grid node -- way/201845280-765 (Wardha, 14 km)</t>
+  </si>
+  <si>
+    <t>UP,LO</t>
+  </si>
+  <si>
+    <t>act_bnd</t>
   </si>
 </sst>
 </file>
@@ -9937,7 +9943,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A64C410-895F-4040-A7AB-3F7211AA7FBD}">
-  <dimension ref="B1:N42"/>
+  <dimension ref="B1:N43"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="11.42578125" style="11"/>
@@ -10090,49 +10096,52 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="2:12">
-      <c r="B14" s="14" t="s">
+    <row r="12" spans="2:12">
+      <c r="C12" s="11" t="s">
+        <v>648</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>649</v>
+      </c>
+      <c r="E12" s="11">
+        <v>0</v>
+      </c>
+      <c r="F12" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12">
+      <c r="B15" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="14"/>
-    </row>
-    <row r="15" spans="2:12">
-      <c r="B15" s="15" t="s">
+      <c r="G15" s="14"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="14"/>
+    </row>
+    <row r="16" spans="2:12">
+      <c r="B16" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C16" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="D15" s="15" t="s">
+      <c r="D16" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="E15" s="15" t="s">
+      <c r="E16" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="F15" s="15" t="s">
+      <c r="F16" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="G15" s="15" t="s">
+      <c r="G16" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="H15" s="15" t="s">
+      <c r="H16" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="I15" s="15" t="s">
+      <c r="I16" s="15" t="s">
         <v>56</v>
-      </c>
-    </row>
-    <row r="16" spans="2:12">
-      <c r="D16" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="F16" s="11">
-        <v>2222</v>
-      </c>
-      <c r="G16" s="11" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="17" spans="2:14">
@@ -10140,35 +10149,35 @@
         <v>66</v>
       </c>
       <c r="F17" s="11">
-        <v>8888</v>
+        <v>2222</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="18" spans="2:14" ht="12.75">
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
+        <v>67</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14">
       <c r="D18" s="11" t="s">
-        <v>236</v>
+        <v>66</v>
       </c>
       <c r="F18" s="11">
         <v>8888</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>235</v>
-      </c>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="13"/>
+        <v>234</v>
+      </c>
     </row>
     <row r="19" spans="2:14" ht="12.75">
       <c r="B19" s="13"/>
       <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
+      <c r="D19" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="F19" s="11">
+        <v>8888</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>235</v>
+      </c>
       <c r="H19" s="13"/>
       <c r="I19" s="13"/>
       <c r="J19" s="13"/>
@@ -10184,20 +10193,16 @@
       <c r="I20" s="13"/>
       <c r="J20" s="13"/>
     </row>
-    <row r="21" spans="2:14" ht="15">
-      <c r="B21"/>
-      <c r="C21"/>
-      <c r="D21"/>
-      <c r="E21"/>
-      <c r="F21"/>
-      <c r="G21"/>
-      <c r="H21"/>
-      <c r="I21"/>
-      <c r="J21"/>
-      <c r="K21"/>
-      <c r="L21"/>
-      <c r="M21"/>
-      <c r="N21"/>
+    <row r="21" spans="2:14" ht="12.75">
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="13"/>
+      <c r="J21" s="13"/>
     </row>
     <row r="22" spans="2:14" ht="15">
       <c r="B22"/>
@@ -10513,6 +10518,21 @@
       <c r="L42"/>
       <c r="M42"/>
       <c r="N42"/>
+    </row>
+    <row r="43" spans="2:14" ht="15">
+      <c r="B43"/>
+      <c r="C43"/>
+      <c r="D43"/>
+      <c r="E43"/>
+      <c r="F43"/>
+      <c r="G43"/>
+      <c r="H43"/>
+      <c r="I43"/>
+      <c r="J43"/>
+      <c r="K43"/>
+      <c r="L43"/>
+      <c r="M43"/>
+      <c r="N43"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/VerveStacks_IND_grids_kan10/SysSettings.xlsx
+++ b/VerveStacks_IND_grids_kan10/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C913182-F64E-49ED-81A4-F8F0C953F6A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBBC5EDA-ED95-4C45-B378-C2BD6079E91A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2063" uniqueCount="650">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2061" uniqueCount="648">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -774,7 +774,7 @@
     <t>elc_spv_IND_001</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 1</t>
+    <t>solar electricity near Patan (cluster 1)</t>
   </si>
   <si>
     <t>TWh</t>
@@ -783,1009 +783,1009 @@
     <t>elc_spv_IND_002</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 2</t>
+    <t>solar electricity near Ahor (cluster 2)</t>
   </si>
   <si>
     <t>elc_spv_IND_003</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 3</t>
+    <t>solar electricity near Bhilwara (cluster 3)</t>
   </si>
   <si>
     <t>elc_spv_IND_004</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 4</t>
+    <t>solar electricity near Bhavnagar (cluster 4)</t>
   </si>
   <si>
     <t>elc_spv_IND_005</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 5</t>
+    <t>solar electricity near Godhra (cluster 5)</t>
   </si>
   <si>
     <t>elc_spv_IND_006</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 6</t>
+    <t>solar electricity near Barmhan Kalan (cluster 6)</t>
   </si>
   <si>
     <t>elc_spv_IND_007</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 7</t>
+    <t>solar electricity near Dhulia (cluster 7)</t>
   </si>
   <si>
     <t>elc_spv_IND_008</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 8</t>
+    <t>solar electricity near Amravati (cluster 8)</t>
   </si>
   <si>
     <t>elc_spv_IND_009</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 9</t>
+    <t>solar electricity near Malkapur (cluster 9)</t>
   </si>
   <si>
     <t>elc_spv_IND_010</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 10</t>
+    <t>solar electricity near Ujjain (cluster 10)</t>
   </si>
   <si>
     <t>elc_spv_IND_011</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 11</t>
+    <t>solar electricity near Bhopal (cluster 11)</t>
   </si>
   <si>
     <t>elc_spv_IND_012</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 12</t>
+    <t>solar electricity near Suratgarh (cluster 12)</t>
   </si>
   <si>
     <t>elc_spv_IND_013</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 13</t>
+    <t>solar electricity near Moga (cluster 13)</t>
   </si>
   <si>
     <t>elc_spv_IND_014</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 14</t>
+    <t>solar electricity near Phalodi (cluster 14)</t>
   </si>
   <si>
     <t>elc_spv_IND_015</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 15</t>
+    <t>solar electricity near Fatehpur (cluster 15)</t>
   </si>
   <si>
     <t>elc_spv_IND_016</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 16</t>
+    <t>solar electricity near Pathankot (cluster 16)</t>
   </si>
   <si>
     <t>elc_spv_IND_017</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 17</t>
+    <t>solar electricity near Saharanpur (cluster 17)</t>
   </si>
   <si>
     <t>elc_spv_IND_018</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 18</t>
+    <t>solar electricity near Shivpuri (cluster 18)</t>
   </si>
   <si>
     <t>elc_spv_IND_019</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 19</t>
+    <t>solar electricity near Chhatarpur (cluster 19)</t>
   </si>
   <si>
     <t>elc_spv_IND_020</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 20</t>
+    <t>solar electricity near Kanpur (cluster 20)</t>
   </si>
   <si>
     <t>elc_spv_IND_021</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 21</t>
+    <t>solar electricity near Jaipur (cluster 21)</t>
   </si>
   <si>
     <t>elc_spv_IND_022</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 22</t>
+    <t>solar electricity near Faridabad (cluster 22)</t>
   </si>
   <si>
     <t>elc_spv_IND_023</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 23</t>
+    <t>solar electricity near Haldwani (cluster 23)</t>
   </si>
   <si>
     <t>elc_spv_IND_024</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 24</t>
+    <t>solar electricity near Bareilly (cluster 24)</t>
   </si>
   <si>
     <t>elc_spv_IND_025</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 25</t>
+    <t>solar electricity near Mothihari (cluster 25)</t>
   </si>
   <si>
     <t>elc_spv_IND_026</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 26</t>
+    <t>solar electricity near Bahraigh (cluster 26)</t>
   </si>
   <si>
     <t>elc_spv_IND_027</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 27</t>
+    <t>solar electricity near Prayagraj (cluster 27)</t>
   </si>
   <si>
     <t>elc_spv_IND_028</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 28</t>
+    <t>solar electricity near Ghazipur (cluster 28)</t>
   </si>
   <si>
     <t>elc_spv_IND_029</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 29</t>
+    <t>solar electricity near Jaisalmer (cluster 29)</t>
   </si>
   <si>
     <t>elc_spv_IND_030</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 30</t>
+    <t>solar electricity near Rapar (cluster 30)</t>
   </si>
   <si>
     <t>elc_spv_IND_031</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 31</t>
+    <t>solar electricity near Rajkot (cluster 31)</t>
   </si>
   <si>
     <t>elc_spv_IND_032</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 32</t>
+    <t>solar electricity near Kharagpur (cluster 32)</t>
   </si>
   <si>
     <t>elc_spv_IND_033</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 33</t>
+    <t>solar electricity near Purnea (cluster 33)</t>
   </si>
   <si>
     <t>elc_spv_IND_034</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 34</t>
+    <t>solar electricity near Ingraj Bazar (cluster 34)</t>
   </si>
   <si>
     <t>elc_spv_IND_035</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 35</t>
+    <t>solar electricity near Durgapur (cluster 35)</t>
   </si>
   <si>
     <t>elc_spv_IND_036</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 36</t>
+    <t>solar electricity near Imphal (cluster 36)</t>
   </si>
   <si>
     <t>elc_spv_IND_037</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 37</t>
+    <t>solar electricity near Dimapur (cluster 37)</t>
   </si>
   <si>
     <t>elc_spv_IND_038</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 38</t>
+    <t>solar electricity near Karaikandi (cluster 38)</t>
   </si>
   <si>
     <t>elc_spv_IND_039</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 39</t>
+    <t>solar electricity near Pangzawl (cluster 39)</t>
   </si>
   <si>
     <t>elc_spv_IND_040</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 40</t>
+    <t>solar electricity near Agartala (cluster 40)</t>
   </si>
   <si>
     <t>elc_spv_IND_041</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 41</t>
+    <t>solar electricity near Jorhat (cluster 41)</t>
   </si>
   <si>
     <t>elc_spv_IND_042</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 42</t>
+    <t>solar electricity near Tinsukia (cluster 42)</t>
   </si>
   <si>
     <t>elc_spv_IND_043</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 43</t>
+    <t>solar electricity near Dibrugarh (cluster 43)</t>
   </si>
   <si>
     <t>elc_spv_IND_044</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 44</t>
+    <t>solar electricity near Tura (cluster 44)</t>
   </si>
   <si>
     <t>elc_spv_IND_045</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 45</t>
+    <t>solar electricity near Jalpaiguri (cluster 45)</t>
   </si>
   <si>
     <t>elc_spv_IND_046</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 46</t>
+    <t>solar electricity near Bongaigaon (cluster 46)</t>
   </si>
   <si>
     <t>elc_spv_IND_047</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 47</t>
+    <t>solar electricity near Chicacole (cluster 47)</t>
   </si>
   <si>
     <t>elc_spv_IND_048</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 48</t>
+    <t>solar electricity near Bhubaneshwar (cluster 48)</t>
   </si>
   <si>
     <t>elc_spv_IND_049</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 49</t>
+    <t>solar electricity near Ramgundam (cluster 49)</t>
   </si>
   <si>
     <t>elc_spv_IND_050</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 50</t>
+    <t>solar electricity near Jagdalpur (cluster 50)</t>
   </si>
   <si>
     <t>elc_spv_IND_051</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 51</t>
+    <t>solar electricity near Jagdalpur (cluster 51)</t>
   </si>
   <si>
     <t>elc_spv_IND_052</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 52</t>
+    <t>solar electricity near Mandla (cluster 52)</t>
   </si>
   <si>
     <t>elc_spv_IND_053</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 53</t>
+    <t>solar electricity near Chanda (cluster 53)</t>
   </si>
   <si>
     <t>elc_spv_IND_054</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 54</t>
+    <t>solar electricity near Raipur (cluster 54)</t>
   </si>
   <si>
     <t>elc_spv_IND_055</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 55</t>
+    <t>solar electricity near Bargarh (cluster 55)</t>
   </si>
   <si>
     <t>elc_spv_IND_056</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 56</t>
+    <t>solar electricity near Bada Barabil (cluster 56)</t>
   </si>
   <si>
     <t>elc_spv_IND_057</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 57</t>
+    <t>solar electricity near Ambikapur (cluster 57)</t>
   </si>
   <si>
     <t>elc_spv_IND_058</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 58</t>
+    <t>solar electricity near Gaya (cluster 58)</t>
   </si>
   <si>
     <t>elc_spv_IND_059</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 59</t>
+    <t>solar electricity near Gulbarga (cluster 59)</t>
   </si>
   <si>
     <t>elc_spv_IND_060</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 60</t>
+    <t>solar electricity near Nizamabad (cluster 60)</t>
   </si>
   <si>
     <t>elc_spv_IND_061</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 61</t>
+    <t>solar electricity near Nanded (cluster 61)</t>
   </si>
   <si>
     <t>elc_spv_IND_062</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 62</t>
+    <t>solar electricity near Karjat (cluster 62)</t>
   </si>
   <si>
     <t>elc_spv_IND_063</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 63</t>
+    <t>solar electricity near Belgaum (cluster 63)</t>
   </si>
   <si>
     <t>elc_spv_IND_064</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 64</t>
+    <t>solar electricity near Gadag (cluster 64)</t>
   </si>
   <si>
     <t>elc_spv_IND_065</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 65</t>
+    <t>solar electricity near Rajahmundry (cluster 65)</t>
   </si>
   <si>
     <t>elc_spv_IND_066</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 66</t>
+    <t>solar electricity near Khammam (cluster 66)</t>
   </si>
   <si>
     <t>elc_spv_IND_067</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 67</t>
+    <t>solar electricity near Kadiri (cluster 67)</t>
   </si>
   <si>
     <t>elc_spv_IND_068</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 68</t>
+    <t>solar electricity near Kurnool (cluster 68)</t>
   </si>
   <si>
     <t>elc_spv_IND_069</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 69</t>
+    <t>solar electricity near Arcot (cluster 69)</t>
   </si>
   <si>
     <t>elc_spv_IND_070</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 70</t>
+    <t>solar electricity near Nellore (cluster 70)</t>
   </si>
   <si>
     <t>elc_spv_IND_071</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 71</t>
+    <t>solar electricity near Paramagudi (cluster 71)</t>
   </si>
   <si>
     <t>elc_spv_IND_072</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 72</t>
+    <t>solar electricity near Tanjore (cluster 72)</t>
   </si>
   <si>
     <t>elc_spv_IND_073</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 73</t>
+    <t>solar electricity near Trichinopoly (cluster 73)</t>
   </si>
   <si>
     <t>elc_spv_IND_074</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 74</t>
+    <t>solar electricity near Malappuram (cluster 74)</t>
   </si>
   <si>
     <t>elc_spv_IND_075</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 75</t>
+    <t>solar electricity near Kalleli (cluster 75)</t>
   </si>
   <si>
     <t>elc_spv_IND_076</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 76</t>
+    <t>solar electricity near Mangalore (cluster 76)</t>
   </si>
   <si>
     <t>elc_spv_IND_077</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 77</t>
+    <t>solar electricity near Chamrajnagar (cluster 77)</t>
   </si>
   <si>
     <t>elc_spv_IND_078</t>
   </si>
   <si>
-    <t>solar electricity generation in cluster -- 78</t>
+    <t>solar electricity near Arsikere (cluster 78)</t>
   </si>
   <si>
     <t>elc_wof_IND_001</t>
   </si>
   <si>
-    <t>wind offshore electricity generation in cluster -- 1</t>
+    <t>wind offshore electricity near Attadappa (cluster 1)</t>
   </si>
   <si>
     <t>elc_wof_IND_002</t>
   </si>
   <si>
-    <t>wind offshore electricity generation in cluster -- 2</t>
+    <t>wind offshore electricity near Mangalore (cluster 2)</t>
   </si>
   <si>
     <t>elc_wof_IND_003</t>
   </si>
   <si>
-    <t>wind offshore electricity generation in cluster -- 3</t>
+    <t>wind offshore electricity near Karwar (cluster 3)</t>
   </si>
   <si>
     <t>elc_wof_IND_004</t>
   </si>
   <si>
-    <t>wind offshore electricity generation in cluster -- 4</t>
+    <t>wind offshore electricity near Ratnagiri (cluster 4)</t>
   </si>
   <si>
     <t>elc_wof_IND_005</t>
   </si>
   <si>
-    <t>wind offshore electricity generation in cluster -- 5</t>
+    <t>wind offshore electricity near Vasco Da Gama (cluster 5)</t>
   </si>
   <si>
     <t>elc_wof_IND_006</t>
   </si>
   <si>
-    <t>wind offshore electricity generation in cluster -- 6</t>
+    <t>wind offshore electricity near Okha (cluster 6)</t>
   </si>
   <si>
     <t>elc_wof_IND_007</t>
   </si>
   <si>
-    <t>wind offshore electricity generation in cluster -- 7</t>
+    <t>wind offshore electricity near Okha (cluster 7)</t>
   </si>
   <si>
     <t>elc_wof_IND_008</t>
   </si>
   <si>
-    <t>wind offshore electricity generation in cluster -- 8</t>
+    <t>wind offshore electricity near Mumbai (cluster 8)</t>
   </si>
   <si>
     <t>elc_wof_IND_009</t>
   </si>
   <si>
-    <t>wind offshore electricity generation in cluster -- 9</t>
+    <t>wind offshore electricity near Veraval (cluster 9)</t>
   </si>
   <si>
     <t>elc_wof_IND_010</t>
   </si>
   <si>
-    <t>wind offshore electricity generation in cluster -- 10</t>
+    <t>wind offshore electricity near Veraval (cluster 10)</t>
   </si>
   <si>
     <t>elc_wof_IND_011</t>
   </si>
   <si>
-    <t>wind offshore electricity generation in cluster -- 11</t>
+    <t>wind offshore electricity near Veraval (cluster 11)</t>
   </si>
   <si>
     <t>elc_wof_IND_012</t>
   </si>
   <si>
-    <t>wind offshore electricity generation in cluster -- 12</t>
+    <t>wind offshore electricity near Mumbai (cluster 12)</t>
   </si>
   <si>
     <t>elc_wof_IND_013</t>
   </si>
   <si>
-    <t>wind offshore electricity generation in cluster -- 13</t>
+    <t>wind offshore electricity near Chennai (cluster 13)</t>
   </si>
   <si>
     <t>elc_wof_IND_014</t>
   </si>
   <si>
-    <t>wind offshore electricity generation in cluster -- 14</t>
+    <t>wind offshore electricity near Negapatam (cluster 14)</t>
   </si>
   <si>
     <t>elc_wof_IND_015</t>
   </si>
   <si>
-    <t>wind offshore electricity generation in cluster -- 15</t>
+    <t>wind offshore electricity near Puducherry (cluster 15)</t>
   </si>
   <si>
     <t>elc_wof_IND_016</t>
   </si>
   <si>
-    <t>wind offshore electricity generation in cluster -- 16</t>
+    <t>wind offshore electricity near Peyanvilai (cluster 16)</t>
   </si>
   <si>
     <t>elc_wof_IND_017</t>
   </si>
   <si>
-    <t>wind offshore electricity generation in cluster -- 17</t>
+    <t>wind offshore electricity near Thiruvananthapuram (cluster 17)</t>
   </si>
   <si>
     <t>elc_wof_IND_018</t>
   </si>
   <si>
-    <t>wind offshore electricity generation in cluster -- 18</t>
+    <t>wind offshore electricity near Nagercoil (cluster 18)</t>
   </si>
   <si>
     <t>elc_wof_IND_019</t>
   </si>
   <si>
-    <t>wind offshore electricity generation in cluster -- 19</t>
+    <t>wind offshore electricity near Ongole (cluster 19)</t>
   </si>
   <si>
     <t>elc_wof_IND_020</t>
   </si>
   <si>
-    <t>wind offshore electricity generation in cluster -- 20</t>
+    <t>wind offshore electricity near Vishakhapatnam (cluster 20)</t>
   </si>
   <si>
     <t>elc_wof_IND_021</t>
   </si>
   <si>
-    <t>wind offshore electricity generation in cluster -- 21</t>
+    <t>wind offshore electricity near Kakinada (cluster 21)</t>
   </si>
   <si>
     <t>elc_wof_IND_022</t>
   </si>
   <si>
-    <t>wind offshore electricity generation in cluster -- 22</t>
+    <t>wind offshore electricity near Haldia (cluster 22)</t>
   </si>
   <si>
     <t>elc_wof_IND_023</t>
   </si>
   <si>
-    <t>wind offshore electricity generation in cluster -- 23</t>
+    <t>wind offshore electricity near Aul (cluster 23)</t>
   </si>
   <si>
     <t>elc_wof_IND_024</t>
   </si>
   <si>
-    <t>wind offshore electricity generation in cluster -- 24</t>
+    <t>wind offshore electricity near Brahmapur (cluster 24)</t>
   </si>
   <si>
     <t>elc_won_IND_001</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 1</t>
+    <t>wind onshore electricity near Sitapur (cluster 1)</t>
   </si>
   <si>
     <t>elc_won_IND_002</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 2</t>
+    <t>wind onshore electricity near Gorakhpur (cluster 2)</t>
   </si>
   <si>
     <t>elc_won_IND_003</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 3</t>
+    <t>wind onshore electricity near Sultanpur (cluster 3)</t>
   </si>
   <si>
     <t>elc_won_IND_004</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 4</t>
+    <t>wind onshore electricity near Moradabad (cluster 4)</t>
   </si>
   <si>
     <t>elc_won_IND_005</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 5</t>
+    <t>wind onshore electricity near Karnal (cluster 5)</t>
   </si>
   <si>
     <t>elc_won_IND_006</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 6</t>
+    <t>wind onshore electricity near Farrukhabad (cluster 6)</t>
   </si>
   <si>
     <t>elc_won_IND_007</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 7</t>
+    <t>wind onshore electricity near Agra (cluster 7)</t>
   </si>
   <si>
     <t>elc_won_IND_008</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 8</t>
+    <t>wind onshore electricity near Delhi (cluster 8)</t>
   </si>
   <si>
     <t>elc_won_IND_009</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 9</t>
+    <t>wind onshore electricity near Katri (cluster 9)</t>
   </si>
   <si>
     <t>elc_won_IND_010</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 10</t>
+    <t>wind onshore electricity near Shahdol (cluster 10)</t>
   </si>
   <si>
     <t>elc_won_IND_011</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 11</t>
+    <t>wind onshore electricity near Sidhi (cluster 11)</t>
   </si>
   <si>
     <t>elc_won_IND_012</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 12</t>
+    <t>wind onshore electricity near Waraseoni (cluster 12)</t>
   </si>
   <si>
     <t>elc_won_IND_013</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 13</t>
+    <t>wind onshore electricity near Mahasamund (cluster 13)</t>
   </si>
   <si>
     <t>elc_won_IND_014</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 14</t>
+    <t>wind onshore electricity near Bhilai (cluster 14)</t>
   </si>
   <si>
     <t>elc_won_IND_015</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 15</t>
+    <t>wind onshore electricity near Jagdalpur (cluster 15)</t>
   </si>
   <si>
     <t>elc_won_IND_016</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 16</t>
+    <t>wind onshore electricity near Mothihari (cluster 16)</t>
   </si>
   <si>
     <t>elc_won_IND_017</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 17</t>
+    <t>wind onshore electricity near Bihta (cluster 17)</t>
   </si>
   <si>
     <t>elc_won_IND_018</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 18</t>
+    <t>wind onshore electricity near Sasaram (cluster 18)</t>
   </si>
   <si>
     <t>elc_won_IND_019</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 19</t>
+    <t>wind onshore electricity near Mirzapur (cluster 19)</t>
   </si>
   <si>
     <t>elc_won_IND_020</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 20</t>
+    <t>wind onshore electricity near Gumla (cluster 20)</t>
   </si>
   <si>
     <t>elc_won_IND_021</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 21</t>
+    <t>wind onshore electricity near Hazaribagh (cluster 21)</t>
   </si>
   <si>
     <t>elc_won_IND_022</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 22</t>
+    <t>wind onshore electricity near Agartala (cluster 22)</t>
   </si>
   <si>
     <t>elc_won_IND_023</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 23</t>
+    <t>wind onshore electricity near Kolkata (cluster 23)</t>
   </si>
   <si>
     <t>elc_won_IND_024</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 24</t>
+    <t>wind onshore electricity near Bhubaneshwar (cluster 24)</t>
   </si>
   <si>
     <t>elc_won_IND_025</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 25</t>
+    <t>wind onshore electricity near Bankura (cluster 25)</t>
   </si>
   <si>
     <t>elc_won_IND_026</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 26</t>
+    <t>wind onshore electricity near Raneswar (cluster 26)</t>
   </si>
   <si>
     <t>elc_won_IND_027</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 27</t>
+    <t>wind onshore electricity near Supaul (cluster 27)</t>
   </si>
   <si>
     <t>elc_won_IND_028</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 28</t>
+    <t>wind onshore electricity near Balurghat (cluster 28)</t>
   </si>
   <si>
     <t>elc_won_IND_029</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 29</t>
+    <t>wind onshore electricity near Peruvancha (cluster 29)</t>
   </si>
   <si>
     <t>elc_won_IND_030</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 30</t>
+    <t>wind onshore electricity near Ongole (cluster 30)</t>
   </si>
   <si>
     <t>elc_won_IND_031</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 31</t>
+    <t>wind onshore electricity near Kothapet (cluster 31)</t>
   </si>
   <si>
     <t>elc_won_IND_032</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 32</t>
+    <t>wind onshore electricity near Jeypore (cluster 32)</t>
   </si>
   <si>
     <t>elc_won_IND_033</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 33</t>
+    <t>wind onshore electricity near Amravati (cluster 33)</t>
   </si>
   <si>
     <t>elc_won_IND_034</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 34</t>
+    <t>wind onshore electricity near Sirur (cluster 34)</t>
   </si>
   <si>
     <t>elc_won_IND_035</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 35</t>
+    <t>wind onshore electricity near Jalgaon (cluster 35)</t>
   </si>
   <si>
     <t>elc_won_IND_036</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 36</t>
+    <t>wind onshore electricity near Paramagudi (cluster 36)</t>
   </si>
   <si>
     <t>elc_won_IND_037</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 37</t>
+    <t>wind onshore electricity near Oulgaret (cluster 37)</t>
   </si>
   <si>
     <t>elc_won_IND_038</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 38</t>
+    <t>wind onshore electricity near Markapur (cluster 38)</t>
   </si>
   <si>
     <t>elc_won_IND_039</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 39</t>
+    <t>wind onshore electricity near Tiruvannamalai (cluster 39)</t>
   </si>
   <si>
     <t>elc_won_IND_040</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 40</t>
+    <t>wind onshore electricity near Malkajgiri (cluster 40)</t>
   </si>
   <si>
     <t>elc_won_IND_041</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 41</t>
+    <t>wind onshore electricity near Solapur (cluster 41)</t>
   </si>
   <si>
     <t>elc_won_IND_042</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 42</t>
+    <t>wind onshore electricity near Anantapur (cluster 42)</t>
   </si>
   <si>
     <t>elc_won_IND_043</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 43</t>
+    <t>wind onshore electricity near Mahad (cluster 43)</t>
   </si>
   <si>
     <t>elc_won_IND_044</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 44</t>
+    <t>wind onshore electricity near Kolhapur (cluster 44)</t>
   </si>
   <si>
     <t>elc_won_IND_045</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 45</t>
+    <t>wind onshore electricity near Bodinayakkanur (cluster 45)</t>
   </si>
   <si>
     <t>elc_won_IND_046</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 46</t>
+    <t>wind onshore electricity near Mysore (cluster 46)</t>
   </si>
   <si>
     <t>elc_won_IND_047</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 47</t>
+    <t>wind onshore electricity near Hubli (cluster 47)</t>
   </si>
   <si>
     <t>elc_won_IND_048</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 48</t>
+    <t>wind onshore electricity near Gandhidham (cluster 48)</t>
   </si>
   <si>
     <t>elc_won_IND_049</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 49</t>
+    <t>wind onshore electricity near Nasik (cluster 49)</t>
   </si>
   <si>
     <t>elc_won_IND_050</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 50</t>
+    <t>wind onshore electricity near Bhavnagar (cluster 50)</t>
   </si>
   <si>
     <t>elc_won_IND_051</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 51</t>
+    <t>wind onshore electricity near Modasa (cluster 51)</t>
   </si>
   <si>
     <t>elc_won_IND_052</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 52</t>
+    <t>wind onshore electricity near Jodhpur (cluster 52)</t>
   </si>
   <si>
     <t>elc_won_IND_053</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 53</t>
+    <t>wind onshore electricity near Raniwara Kalan (cluster 53)</t>
   </si>
   <si>
     <t>elc_won_IND_054</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 54</t>
+    <t>wind onshore electricity near Gadarwara (cluster 54)</t>
   </si>
   <si>
     <t>elc_won_IND_055</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 55</t>
+    <t>wind onshore electricity near Indore (cluster 55)</t>
   </si>
   <si>
     <t>elc_won_IND_056</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 56</t>
+    <t>wind onshore electricity near Shujalpur (cluster 56)</t>
   </si>
   <si>
     <t>elc_won_IND_057</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 57</t>
+    <t>wind onshore electricity near Bijaynagar (cluster 57)</t>
   </si>
   <si>
     <t>elc_won_IND_058</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 58</t>
+    <t>wind onshore electricity near Sawai Madhopur (cluster 58)</t>
   </si>
   <si>
     <t>elc_won_IND_059</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 59</t>
+    <t>wind onshore electricity near Rath (cluster 59)</t>
   </si>
   <si>
     <t>elc_won_IND_060</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 60</t>
+    <t>wind onshore electricity near Jhansi (cluster 60)</t>
   </si>
   <si>
     <t>elc_won_IND_061</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 61</t>
+    <t>wind onshore electricity near Mansa (cluster 61)</t>
   </si>
   <si>
     <t>elc_won_IND_062</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 62</t>
+    <t>wind onshore electricity near Alwar (cluster 62)</t>
   </si>
   <si>
     <t>elc_won_IND_063</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 63</t>
+    <t>wind onshore electricity near Hisar (cluster 63)</t>
   </si>
   <si>
     <t>elc_won_IND_064</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 64</t>
+    <t>wind onshore electricity near Jaisalmer (cluster 64)</t>
   </si>
   <si>
     <t>elc_won_IND_065</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 65</t>
+    <t>wind onshore electricity near Suratgarh (cluster 65)</t>
   </si>
   <si>
     <t>elc_won_IND_066</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 66</t>
+    <t>wind onshore electricity near Sikar (cluster 66)</t>
   </si>
   <si>
     <t>elc_won_IND_067</t>
   </si>
   <si>
-    <t>onshore wind electricity generation in cluster -- 67</t>
+    <t>wind onshore electricity near Nokha (cluster 67)</t>
   </si>
   <si>
     <t>~fi_comm</t>
@@ -1984,12 +1984,6 @@
   </si>
   <si>
     <t>heat at grid node -- way/201845280-765 (Wardha, 14 km)</t>
-  </si>
-  <si>
-    <t>UP,LO</t>
-  </si>
-  <si>
-    <t>act_bnd</t>
   </si>
 </sst>
 </file>
@@ -4404,7 +4398,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16D456FC-24B3-4CB5-9753-241A2423764F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7E802A2-4CBF-4D8B-AFA2-EB2B6E5CF376}">
   <dimension ref="B3:I20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -4861,7 +4855,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D9599A1-DD50-435D-BF2E-C3A4946395B4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64C12774-3FAA-4C7B-832F-87F6F02D52A5}">
   <dimension ref="B3:I20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -9943,7 +9937,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A64C410-895F-4040-A7AB-3F7211AA7FBD}">
-  <dimension ref="B1:N43"/>
+  <dimension ref="B1:N42"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="11.42578125" style="11"/>
@@ -10096,52 +10090,49 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="2:12">
-      <c r="C12" s="11" t="s">
-        <v>648</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>649</v>
-      </c>
-      <c r="E12" s="11">
-        <v>0</v>
-      </c>
-      <c r="F12" s="11">
-        <v>3</v>
-      </c>
+    <row r="14" spans="2:12">
+      <c r="B14" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="14"/>
     </row>
     <row r="15" spans="2:12">
-      <c r="B15" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="14"/>
+      <c r="B15" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="F15" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="G15" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="H15" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="I15" s="15" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="16" spans="2:12">
-      <c r="B16" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="C16" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="D16" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="E16" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="G16" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="H16" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="I16" s="15" t="s">
-        <v>56</v>
+      <c r="D16" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="F16" s="11">
+        <v>2222</v>
+      </c>
+      <c r="G16" s="11" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="17" spans="2:14">
@@ -10149,35 +10140,35 @@
         <v>66</v>
       </c>
       <c r="F17" s="11">
-        <v>2222</v>
+        <v>8888</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="18" spans="2:14">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14" ht="12.75">
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
       <c r="D18" s="11" t="s">
-        <v>66</v>
+        <v>236</v>
       </c>
       <c r="F18" s="11">
         <v>8888</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>234</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="H18" s="13"/>
+      <c r="I18" s="13"/>
+      <c r="J18" s="13"/>
     </row>
     <row r="19" spans="2:14" ht="12.75">
       <c r="B19" s="13"/>
       <c r="C19" s="13"/>
-      <c r="D19" s="11" t="s">
-        <v>236</v>
-      </c>
-      <c r="F19" s="11">
-        <v>8888</v>
-      </c>
-      <c r="G19" s="11" t="s">
-        <v>235</v>
-      </c>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
       <c r="H19" s="13"/>
       <c r="I19" s="13"/>
       <c r="J19" s="13"/>
@@ -10193,16 +10184,20 @@
       <c r="I20" s="13"/>
       <c r="J20" s="13"/>
     </row>
-    <row r="21" spans="2:14" ht="12.75">
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="13"/>
-      <c r="J21" s="13"/>
+    <row r="21" spans="2:14" ht="15">
+      <c r="B21"/>
+      <c r="C21"/>
+      <c r="D21"/>
+      <c r="E21"/>
+      <c r="F21"/>
+      <c r="G21"/>
+      <c r="H21"/>
+      <c r="I21"/>
+      <c r="J21"/>
+      <c r="K21"/>
+      <c r="L21"/>
+      <c r="M21"/>
+      <c r="N21"/>
     </row>
     <row r="22" spans="2:14" ht="15">
       <c r="B22"/>
@@ -10518,21 +10513,6 @@
       <c r="L42"/>
       <c r="M42"/>
       <c r="N42"/>
-    </row>
-    <row r="43" spans="2:14" ht="15">
-      <c r="B43"/>
-      <c r="C43"/>
-      <c r="D43"/>
-      <c r="E43"/>
-      <c r="F43"/>
-      <c r="G43"/>
-      <c r="H43"/>
-      <c r="I43"/>
-      <c r="J43"/>
-      <c r="K43"/>
-      <c r="L43"/>
-      <c r="M43"/>
-      <c r="N43"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/VerveStacks_IND_grids_kan10/SysSettings.xlsx
+++ b/VerveStacks_IND_grids_kan10/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBBC5EDA-ED95-4C45-B378-C2BD6079E91A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E24BBDC-62D7-46E7-8001-94FBF513A54D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4398,7 +4398,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7E802A2-4CBF-4D8B-AFA2-EB2B6E5CF376}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37AC575F-2E7D-4548-A9CA-D3B4EAC78D00}">
   <dimension ref="B3:I20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -4855,7 +4855,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64C12774-3FAA-4C7B-832F-87F6F02D52A5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF70EA25-F084-476B-8575-FF9CBC45EB17}">
   <dimension ref="B3:I20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>

--- a/VerveStacks_IND_grids_kan10/SysSettings.xlsx
+++ b/VerveStacks_IND_grids_kan10/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E24BBDC-62D7-46E7-8001-94FBF513A54D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23FE86FD-A724-4BD9-9C75-FDCC7F5E7579}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2061" uniqueCount="648">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2054" uniqueCount="646">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -774,7 +774,7 @@
     <t>elc_spv_IND_001</t>
   </si>
   <si>
-    <t>solar electricity near Patan (cluster 1)</t>
+    <t>solar electricity near Tinkhang (cluster 1)</t>
   </si>
   <si>
     <t>TWh</t>
@@ -783,295 +783,295 @@
     <t>elc_spv_IND_002</t>
   </si>
   <si>
-    <t>solar electricity near Ahor (cluster 2)</t>
+    <t>solar electricity near Tinsukia (cluster 2)</t>
   </si>
   <si>
     <t>elc_spv_IND_003</t>
   </si>
   <si>
-    <t>solar electricity near Bhilwara (cluster 3)</t>
+    <t>solar electricity near Sibsagar (cluster 3)</t>
   </si>
   <si>
     <t>elc_spv_IND_004</t>
   </si>
   <si>
-    <t>solar electricity near Bhavnagar (cluster 4)</t>
+    <t>solar electricity near Guwahati (cluster 4)</t>
   </si>
   <si>
     <t>elc_spv_IND_005</t>
   </si>
   <si>
-    <t>solar electricity near Godhra (cluster 5)</t>
+    <t>solar electricity near Tura (cluster 5)</t>
   </si>
   <si>
     <t>elc_spv_IND_006</t>
   </si>
   <si>
-    <t>solar electricity near Barmhan Kalan (cluster 6)</t>
+    <t>solar electricity near Koch Bihar (cluster 6)</t>
   </si>
   <si>
     <t>elc_spv_IND_007</t>
   </si>
   <si>
-    <t>solar electricity near Dhulia (cluster 7)</t>
+    <t>solar electricity near Pangzawl (cluster 7)</t>
   </si>
   <si>
     <t>elc_spv_IND_008</t>
   </si>
   <si>
-    <t>solar electricity near Amravati (cluster 8)</t>
+    <t>solar electricity near Agartala (cluster 8)</t>
   </si>
   <si>
     <t>elc_spv_IND_009</t>
   </si>
   <si>
-    <t>solar electricity near Malkapur (cluster 9)</t>
+    <t>solar electricity near Nowgong (cluster 9)</t>
   </si>
   <si>
     <t>elc_spv_IND_010</t>
   </si>
   <si>
-    <t>solar electricity near Ujjain (cluster 10)</t>
+    <t>solar electricity near Dimapur (cluster 10)</t>
   </si>
   <si>
     <t>elc_spv_IND_011</t>
   </si>
   <si>
-    <t>solar electricity near Bhopal (cluster 11)</t>
+    <t>solar electricity near Karaikandi (cluster 11)</t>
   </si>
   <si>
     <t>elc_spv_IND_012</t>
   </si>
   <si>
-    <t>solar electricity near Suratgarh (cluster 12)</t>
+    <t>solar electricity near Imphal (cluster 12)</t>
   </si>
   <si>
     <t>elc_spv_IND_013</t>
   </si>
   <si>
-    <t>solar electricity near Moga (cluster 13)</t>
+    <t>solar electricity near Satna (cluster 13)</t>
   </si>
   <si>
     <t>elc_spv_IND_014</t>
   </si>
   <si>
-    <t>solar electricity near Phalodi (cluster 14)</t>
+    <t>solar electricity near Bahraigh (cluster 14)</t>
   </si>
   <si>
     <t>elc_spv_IND_015</t>
   </si>
   <si>
-    <t>solar electricity near Fatehpur (cluster 15)</t>
+    <t>solar electricity near Orai (cluster 15)</t>
   </si>
   <si>
     <t>elc_spv_IND_016</t>
   </si>
   <si>
-    <t>solar electricity near Pathankot (cluster 16)</t>
+    <t>solar electricity near Prayagraj (cluster 16)</t>
   </si>
   <si>
     <t>elc_spv_IND_017</t>
   </si>
   <si>
-    <t>solar electricity near Saharanpur (cluster 17)</t>
+    <t>solar electricity near Bettiah (cluster 17)</t>
   </si>
   <si>
     <t>elc_spv_IND_018</t>
   </si>
   <si>
-    <t>solar electricity near Shivpuri (cluster 18)</t>
+    <t>solar electricity near Karamdiha (cluster 18)</t>
   </si>
   <si>
     <t>elc_spv_IND_019</t>
   </si>
   <si>
-    <t>solar electricity near Chhatarpur (cluster 19)</t>
+    <t>solar electricity near Khurda (cluster 19)</t>
   </si>
   <si>
     <t>elc_spv_IND_020</t>
   </si>
   <si>
-    <t>solar electricity near Kanpur (cluster 20)</t>
+    <t>solar electricity near Soro (cluster 20)</t>
   </si>
   <si>
     <t>elc_spv_IND_021</t>
   </si>
   <si>
-    <t>solar electricity near Jaipur (cluster 21)</t>
+    <t>solar electricity near Balangir (cluster 21)</t>
   </si>
   <si>
     <t>elc_spv_IND_022</t>
   </si>
   <si>
-    <t>solar electricity near Faridabad (cluster 22)</t>
+    <t>solar electricity near Raurkela (cluster 22)</t>
   </si>
   <si>
     <t>elc_spv_IND_023</t>
   </si>
   <si>
-    <t>solar electricity near Haldwani (cluster 23)</t>
+    <t>solar electricity near Purnea (cluster 23)</t>
   </si>
   <si>
     <t>elc_spv_IND_024</t>
   </si>
   <si>
-    <t>solar electricity near Bareilly (cluster 24)</t>
+    <t>solar electricity near Katoya (cluster 24)</t>
   </si>
   <si>
     <t>elc_spv_IND_025</t>
   </si>
   <si>
-    <t>solar electricity near Mothihari (cluster 25)</t>
+    <t>solar electricity near Ingraj Bazar (cluster 25)</t>
   </si>
   <si>
     <t>elc_spv_IND_026</t>
   </si>
   <si>
-    <t>solar electricity near Bahraigh (cluster 26)</t>
+    <t>solar electricity near Kolkata (cluster 26)</t>
   </si>
   <si>
     <t>elc_spv_IND_027</t>
   </si>
   <si>
-    <t>solar electricity near Prayagraj (cluster 27)</t>
+    <t>solar electricity near Jamshedpur (cluster 27)</t>
   </si>
   <si>
     <t>elc_spv_IND_028</t>
   </si>
   <si>
-    <t>solar electricity near Ghazipur (cluster 28)</t>
+    <t>solar electricity near Koiridih (cluster 28)</t>
   </si>
   <si>
     <t>elc_spv_IND_029</t>
   </si>
   <si>
-    <t>solar electricity near Jaisalmer (cluster 29)</t>
+    <t>solar electricity near Trichinopoly (cluster 29)</t>
   </si>
   <si>
     <t>elc_spv_IND_030</t>
   </si>
   <si>
-    <t>solar electricity near Rapar (cluster 30)</t>
+    <t>solar electricity near Kalleli (cluster 30)</t>
   </si>
   <si>
     <t>elc_spv_IND_031</t>
   </si>
   <si>
-    <t>solar electricity near Rajkot (cluster 31)</t>
+    <t>solar electricity near Nadampalaiyam (cluster 31)</t>
   </si>
   <si>
     <t>elc_spv_IND_032</t>
   </si>
   <si>
-    <t>solar electricity near Kharagpur (cluster 32)</t>
+    <t>solar electricity near Salem (cluster 32)</t>
   </si>
   <si>
     <t>elc_spv_IND_033</t>
   </si>
   <si>
-    <t>solar electricity near Purnea (cluster 33)</t>
+    <t>solar electricity near Vizianagaram (cluster 33)</t>
   </si>
   <si>
     <t>elc_spv_IND_034</t>
   </si>
   <si>
-    <t>solar electricity near Ingraj Bazar (cluster 34)</t>
+    <t>solar electricity near Vijayawada (cluster 34)</t>
   </si>
   <si>
     <t>elc_spv_IND_035</t>
   </si>
   <si>
-    <t>solar electricity near Durgapur (cluster 35)</t>
+    <t>solar electricity near Raichur (cluster 35)</t>
   </si>
   <si>
     <t>elc_spv_IND_036</t>
   </si>
   <si>
-    <t>solar electricity near Imphal (cluster 36)</t>
+    <t>solar electricity near Nandyal (cluster 36)</t>
   </si>
   <si>
     <t>elc_spv_IND_037</t>
   </si>
   <si>
-    <t>solar electricity near Dimapur (cluster 37)</t>
+    <t>solar electricity near Conjeeveram (cluster 37)</t>
   </si>
   <si>
     <t>elc_spv_IND_038</t>
   </si>
   <si>
-    <t>solar electricity near Karaikandi (cluster 38)</t>
+    <t>solar electricity near Nellore (cluster 38)</t>
   </si>
   <si>
     <t>elc_spv_IND_039</t>
   </si>
   <si>
-    <t>solar electricity near Pangzawl (cluster 39)</t>
+    <t>solar electricity near Madanapalle (cluster 39)</t>
   </si>
   <si>
     <t>elc_spv_IND_040</t>
   </si>
   <si>
-    <t>solar electricity near Agartala (cluster 40)</t>
+    <t>solar electricity near Ahmadnagar (cluster 40)</t>
   </si>
   <si>
     <t>elc_spv_IND_041</t>
   </si>
   <si>
-    <t>solar electricity near Jorhat (cluster 41)</t>
+    <t>solar electricity near Mahad (cluster 41)</t>
   </si>
   <si>
     <t>elc_spv_IND_042</t>
   </si>
   <si>
-    <t>solar electricity near Tinsukia (cluster 42)</t>
+    <t>solar electricity near Nanded (cluster 42)</t>
   </si>
   <si>
     <t>elc_spv_IND_043</t>
   </si>
   <si>
-    <t>solar electricity near Dibrugarh (cluster 43)</t>
+    <t>solar electricity near Solapur (cluster 43)</t>
   </si>
   <si>
     <t>elc_spv_IND_044</t>
   </si>
   <si>
-    <t>solar electricity near Tura (cluster 44)</t>
+    <t>solar electricity near Belgaum (cluster 44)</t>
   </si>
   <si>
     <t>elc_spv_IND_045</t>
   </si>
   <si>
-    <t>solar electricity near Jalpaiguri (cluster 45)</t>
+    <t>solar electricity near Gadag (cluster 45)</t>
   </si>
   <si>
     <t>elc_spv_IND_046</t>
   </si>
   <si>
-    <t>solar electricity near Bongaigaon (cluster 46)</t>
+    <t>solar electricity near Tumkur (cluster 46)</t>
   </si>
   <si>
     <t>elc_spv_IND_047</t>
   </si>
   <si>
-    <t>solar electricity near Chicacole (cluster 47)</t>
+    <t>solar electricity near Mangalore (cluster 47)</t>
   </si>
   <si>
     <t>elc_spv_IND_048</t>
   </si>
   <si>
-    <t>solar electricity near Bhubaneshwar (cluster 48)</t>
+    <t>solar electricity near Seoni (cluster 48)</t>
   </si>
   <si>
     <t>elc_spv_IND_049</t>
   </si>
   <si>
-    <t>solar electricity near Ramgundam (cluster 49)</t>
+    <t>solar electricity near Pali (cluster 49)</t>
   </si>
   <si>
     <t>elc_spv_IND_050</t>
   </si>
   <si>
-    <t>solar electricity near Jagdalpur (cluster 50)</t>
+    <t>solar electricity near Raipur (cluster 50)</t>
   </si>
   <si>
     <t>elc_spv_IND_051</t>
@@ -1083,7 +1083,7 @@
     <t>elc_spv_IND_052</t>
   </si>
   <si>
-    <t>solar electricity near Mandla (cluster 52)</t>
+    <t>solar electricity near Jagdalpur (cluster 52)</t>
   </si>
   <si>
     <t>elc_spv_IND_053</t>
@@ -1095,205 +1095,205 @@
     <t>elc_spv_IND_054</t>
   </si>
   <si>
-    <t>solar electricity near Raipur (cluster 54)</t>
+    <t>solar electricity near Warangal (cluster 54)</t>
   </si>
   <si>
     <t>elc_spv_IND_055</t>
   </si>
   <si>
-    <t>solar electricity near Bargarh (cluster 55)</t>
+    <t>solar electricity near Rajsamand (cluster 55)</t>
   </si>
   <si>
     <t>elc_spv_IND_056</t>
   </si>
   <si>
-    <t>solar electricity near Bada Barabil (cluster 56)</t>
+    <t>solar electricity near Bhavnagar (cluster 56)</t>
   </si>
   <si>
     <t>elc_spv_IND_057</t>
   </si>
   <si>
-    <t>solar electricity near Ambikapur (cluster 57)</t>
+    <t>solar electricity near Dhrangadhra (cluster 57)</t>
   </si>
   <si>
     <t>elc_spv_IND_058</t>
   </si>
   <si>
-    <t>solar electricity near Gaya (cluster 58)</t>
+    <t>solar electricity near Saila (cluster 58)</t>
   </si>
   <si>
     <t>elc_spv_IND_059</t>
   </si>
   <si>
-    <t>solar electricity near Gulbarga (cluster 59)</t>
+    <t>solar electricity near Bhuj (cluster 59)</t>
   </si>
   <si>
     <t>elc_spv_IND_060</t>
   </si>
   <si>
-    <t>solar electricity near Nizamabad (cluster 60)</t>
+    <t>solar electricity near Jalna (cluster 60)</t>
   </si>
   <si>
     <t>elc_spv_IND_061</t>
   </si>
   <si>
-    <t>solar electricity near Nanded (cluster 61)</t>
+    <t>solar electricity near Amravati (cluster 61)</t>
   </si>
   <si>
     <t>elc_spv_IND_062</t>
   </si>
   <si>
-    <t>solar electricity near Karjat (cluster 62)</t>
+    <t>solar electricity near Wapi (cluster 62)</t>
   </si>
   <si>
     <t>elc_spv_IND_063</t>
   </si>
   <si>
-    <t>solar electricity near Belgaum (cluster 63)</t>
+    <t>solar electricity near Dhulia (cluster 63)</t>
   </si>
   <si>
     <t>elc_spv_IND_064</t>
   </si>
   <si>
-    <t>solar electricity near Gadag (cluster 64)</t>
+    <t>solar electricity near Godhra (cluster 64)</t>
   </si>
   <si>
     <t>elc_spv_IND_065</t>
   </si>
   <si>
-    <t>solar electricity near Rajahmundry (cluster 65)</t>
+    <t>solar electricity near Ujjain (cluster 65)</t>
   </si>
   <si>
     <t>elc_spv_IND_066</t>
   </si>
   <si>
-    <t>solar electricity near Khammam (cluster 66)</t>
+    <t>solar electricity near Saugor (cluster 66)</t>
   </si>
   <si>
     <t>elc_spv_IND_067</t>
   </si>
   <si>
-    <t>solar electricity near Kadiri (cluster 67)</t>
+    <t>solar electricity near Jhansi (cluster 67)</t>
   </si>
   <si>
     <t>elc_spv_IND_068</t>
   </si>
   <si>
-    <t>solar electricity near Kurnool (cluster 68)</t>
+    <t>solar electricity near Kota (cluster 68)</t>
   </si>
   <si>
     <t>elc_spv_IND_069</t>
   </si>
   <si>
-    <t>solar electricity near Arcot (cluster 69)</t>
+    <t>solar electricity near Kashipur (cluster 69)</t>
   </si>
   <si>
     <t>elc_spv_IND_070</t>
   </si>
   <si>
-    <t>solar electricity near Nellore (cluster 70)</t>
+    <t>solar electricity near Bareilly (cluster 70)</t>
   </si>
   <si>
     <t>elc_spv_IND_071</t>
   </si>
   <si>
-    <t>solar electricity near Paramagudi (cluster 71)</t>
+    <t>solar electricity near Aligarh (cluster 71)</t>
   </si>
   <si>
     <t>elc_spv_IND_072</t>
   </si>
   <si>
-    <t>solar electricity near Tanjore (cluster 72)</t>
+    <t>solar electricity near Jaipur (cluster 72)</t>
   </si>
   <si>
     <t>elc_spv_IND_073</t>
   </si>
   <si>
-    <t>solar electricity near Trichinopoly (cluster 73)</t>
+    <t>solar electricity near Sikar (cluster 73)</t>
   </si>
   <si>
     <t>elc_spv_IND_074</t>
   </si>
   <si>
-    <t>solar electricity near Malappuram (cluster 74)</t>
+    <t>solar electricity near Bikaner (cluster 74)</t>
   </si>
   <si>
     <t>elc_spv_IND_075</t>
   </si>
   <si>
-    <t>solar electricity near Kalleli (cluster 75)</t>
+    <t>solar electricity near Jaisalmer (cluster 75)</t>
   </si>
   <si>
     <t>elc_spv_IND_076</t>
   </si>
   <si>
-    <t>solar electricity near Mangalore (cluster 76)</t>
+    <t>solar electricity near Bhatinda (cluster 76)</t>
   </si>
   <si>
     <t>elc_spv_IND_077</t>
   </si>
   <si>
-    <t>solar electricity near Chamrajnagar (cluster 77)</t>
+    <t>solar electricity near Pathankot (cluster 77)</t>
   </si>
   <si>
     <t>elc_spv_IND_078</t>
   </si>
   <si>
-    <t>solar electricity near Arsikere (cluster 78)</t>
+    <t>solar electricity near Chandigarh (cluster 78)</t>
   </si>
   <si>
     <t>elc_wof_IND_001</t>
   </si>
   <si>
-    <t>wind offshore electricity near Attadappa (cluster 1)</t>
+    <t>wind offshore electricity near Mangalore (cluster 1)</t>
   </si>
   <si>
     <t>elc_wof_IND_002</t>
   </si>
   <si>
-    <t>wind offshore electricity near Mangalore (cluster 2)</t>
+    <t>wind offshore electricity near Karwar (cluster 2)</t>
   </si>
   <si>
     <t>elc_wof_IND_003</t>
   </si>
   <si>
-    <t>wind offshore electricity near Karwar (cluster 3)</t>
+    <t>wind offshore electricity near Ratnagiri (cluster 3)</t>
   </si>
   <si>
     <t>elc_wof_IND_004</t>
   </si>
   <si>
-    <t>wind offshore electricity near Ratnagiri (cluster 4)</t>
+    <t>wind offshore electricity near Porbandar (cluster 4)</t>
   </si>
   <si>
     <t>elc_wof_IND_005</t>
   </si>
   <si>
-    <t>wind offshore electricity near Vasco Da Gama (cluster 5)</t>
+    <t>wind offshore electricity near Okha (cluster 5)</t>
   </si>
   <si>
     <t>elc_wof_IND_006</t>
   </si>
   <si>
-    <t>wind offshore electricity near Okha (cluster 6)</t>
+    <t>wind offshore electricity near Mumbai (cluster 6)</t>
   </si>
   <si>
     <t>elc_wof_IND_007</t>
   </si>
   <si>
-    <t>wind offshore electricity near Okha (cluster 7)</t>
+    <t>wind offshore electricity near Ratnagiri (cluster 7)</t>
   </si>
   <si>
     <t>elc_wof_IND_008</t>
   </si>
   <si>
-    <t>wind offshore electricity near Mumbai (cluster 8)</t>
+    <t>wind offshore electricity near Veraval (cluster 8)</t>
   </si>
   <si>
     <t>elc_wof_IND_009</t>
   </si>
   <si>
-    <t>wind offshore electricity near Veraval (cluster 9)</t>
+    <t>wind offshore electricity near Mumbai (cluster 9)</t>
   </si>
   <si>
     <t>elc_wof_IND_010</t>
@@ -1305,31 +1305,31 @@
     <t>elc_wof_IND_011</t>
   </si>
   <si>
-    <t>wind offshore electricity near Veraval (cluster 11)</t>
+    <t>wind offshore electricity near Haldia (cluster 11)</t>
   </si>
   <si>
     <t>elc_wof_IND_012</t>
   </si>
   <si>
-    <t>wind offshore electricity near Mumbai (cluster 12)</t>
+    <t>wind offshore electricity near Haldia (cluster 12)</t>
   </si>
   <si>
     <t>elc_wof_IND_013</t>
   </si>
   <si>
-    <t>wind offshore electricity near Chennai (cluster 13)</t>
+    <t>wind offshore electricity near Chicacole (cluster 13)</t>
   </si>
   <si>
     <t>elc_wof_IND_014</t>
   </si>
   <si>
-    <t>wind offshore electricity near Negapatam (cluster 14)</t>
+    <t>wind offshore electricity near Aul (cluster 14)</t>
   </si>
   <si>
     <t>elc_wof_IND_015</t>
   </si>
   <si>
-    <t>wind offshore electricity near Puducherry (cluster 15)</t>
+    <t>wind offshore electricity near Brahmapur (cluster 15)</t>
   </si>
   <si>
     <t>elc_wof_IND_016</t>
@@ -1341,451 +1341,445 @@
     <t>elc_wof_IND_017</t>
   </si>
   <si>
-    <t>wind offshore electricity near Thiruvananthapuram (cluster 17)</t>
+    <t>wind offshore electricity near Nagercoil (cluster 17)</t>
   </si>
   <si>
     <t>elc_wof_IND_018</t>
   </si>
   <si>
-    <t>wind offshore electricity near Nagercoil (cluster 18)</t>
+    <t>wind offshore electricity near Thiruvananthapuram (cluster 18)</t>
   </si>
   <si>
     <t>elc_wof_IND_019</t>
   </si>
   <si>
-    <t>wind offshore electricity near Ongole (cluster 19)</t>
+    <t>wind offshore electricity near Chennai (cluster 19)</t>
   </si>
   <si>
     <t>elc_wof_IND_020</t>
   </si>
   <si>
-    <t>wind offshore electricity near Vishakhapatnam (cluster 20)</t>
+    <t>wind offshore electricity near Negapatam (cluster 20)</t>
   </si>
   <si>
     <t>elc_wof_IND_021</t>
   </si>
   <si>
-    <t>wind offshore electricity near Kakinada (cluster 21)</t>
+    <t>wind offshore electricity near Oulgaret (cluster 21)</t>
   </si>
   <si>
     <t>elc_wof_IND_022</t>
   </si>
   <si>
-    <t>wind offshore electricity near Haldia (cluster 22)</t>
+    <t>wind offshore electricity near Kakinada (cluster 22)</t>
   </si>
   <si>
     <t>elc_wof_IND_023</t>
   </si>
   <si>
-    <t>wind offshore electricity near Aul (cluster 23)</t>
+    <t>wind offshore electricity near Nellore (cluster 23)</t>
   </si>
   <si>
     <t>elc_wof_IND_024</t>
   </si>
   <si>
-    <t>wind offshore electricity near Brahmapur (cluster 24)</t>
+    <t>wind offshore electricity near Ongole (cluster 24)</t>
   </si>
   <si>
     <t>elc_won_IND_001</t>
   </si>
   <si>
-    <t>wind onshore electricity near Sitapur (cluster 1)</t>
+    <t>wind onshore electricity near Raipur (cluster 1)</t>
   </si>
   <si>
     <t>elc_won_IND_002</t>
   </si>
   <si>
-    <t>wind onshore electricity near Gorakhpur (cluster 2)</t>
+    <t>wind onshore electricity near Bhilai (cluster 2)</t>
   </si>
   <si>
     <t>elc_won_IND_003</t>
   </si>
   <si>
-    <t>wind onshore electricity near Sultanpur (cluster 3)</t>
+    <t>wind onshore electricity near Multai (cluster 3)</t>
   </si>
   <si>
     <t>elc_won_IND_004</t>
   </si>
   <si>
-    <t>wind onshore electricity near Moradabad (cluster 4)</t>
+    <t>wind onshore electricity near Chhindwara (cluster 4)</t>
   </si>
   <si>
     <t>elc_won_IND_005</t>
   </si>
   <si>
-    <t>wind onshore electricity near Karnal (cluster 5)</t>
+    <t>wind onshore electricity near Kakinada (cluster 5)</t>
   </si>
   <si>
     <t>elc_won_IND_006</t>
   </si>
   <si>
-    <t>wind onshore electricity near Farrukhabad (cluster 6)</t>
+    <t>wind onshore electricity near Vijayawada (cluster 6)</t>
   </si>
   <si>
     <t>elc_won_IND_007</t>
   </si>
   <si>
-    <t>wind onshore electricity near Agra (cluster 7)</t>
+    <t>wind onshore electricity near Warangal (cluster 7)</t>
   </si>
   <si>
     <t>elc_won_IND_008</t>
   </si>
   <si>
-    <t>wind onshore electricity near Delhi (cluster 8)</t>
+    <t>wind onshore electricity near Jeypore (cluster 8)</t>
   </si>
   <si>
     <t>elc_won_IND_009</t>
   </si>
   <si>
-    <t>wind onshore electricity near Katri (cluster 9)</t>
+    <t>wind onshore electricity near Yavatmal (cluster 9)</t>
   </si>
   <si>
     <t>elc_won_IND_010</t>
   </si>
   <si>
-    <t>wind onshore electricity near Shahdol (cluster 10)</t>
+    <t>wind onshore electricity near Chanda (cluster 10)</t>
   </si>
   <si>
     <t>elc_won_IND_011</t>
   </si>
   <si>
-    <t>wind onshore electricity near Sidhi (cluster 11)</t>
+    <t>wind onshore electricity near Mahad (cluster 11)</t>
   </si>
   <si>
     <t>elc_won_IND_012</t>
   </si>
   <si>
-    <t>wind onshore electricity near Waraseoni (cluster 12)</t>
+    <t>wind onshore electricity near Belgaum (cluster 12)</t>
   </si>
   <si>
     <t>elc_won_IND_013</t>
   </si>
   <si>
-    <t>wind onshore electricity near Mahasamund (cluster 13)</t>
+    <t>wind onshore electricity near Mysore (cluster 13)</t>
   </si>
   <si>
     <t>elc_won_IND_014</t>
   </si>
   <si>
-    <t>wind onshore electricity near Bhilai (cluster 14)</t>
+    <t>wind onshore electricity near Cuddapah (cluster 14)</t>
   </si>
   <si>
     <t>elc_won_IND_015</t>
   </si>
   <si>
-    <t>wind onshore electricity near Jagdalpur (cluster 15)</t>
+    <t>wind onshore electricity near Hyderabad (cluster 15)</t>
   </si>
   <si>
     <t>elc_won_IND_016</t>
   </si>
   <si>
-    <t>wind onshore electricity near Mothihari (cluster 16)</t>
+    <t>wind onshore electricity near Gulbarga (cluster 16)</t>
   </si>
   <si>
     <t>elc_won_IND_017</t>
   </si>
   <si>
-    <t>wind onshore electricity near Bihta (cluster 17)</t>
+    <t>wind onshore electricity near Sirur (cluster 17)</t>
   </si>
   <si>
     <t>elc_won_IND_018</t>
   </si>
   <si>
-    <t>wind onshore electricity near Sasaram (cluster 18)</t>
+    <t>wind onshore electricity near Hubli (cluster 18)</t>
   </si>
   <si>
     <t>elc_won_IND_019</t>
   </si>
   <si>
-    <t>wind onshore electricity near Mirzapur (cluster 19)</t>
+    <t>wind onshore electricity near Nellore (cluster 19)</t>
   </si>
   <si>
     <t>elc_won_IND_020</t>
   </si>
   <si>
-    <t>wind onshore electricity near Gumla (cluster 20)</t>
+    <t>wind onshore electricity near Neyveli (cluster 20)</t>
   </si>
   <si>
     <t>elc_won_IND_021</t>
   </si>
   <si>
-    <t>wind onshore electricity near Hazaribagh (cluster 21)</t>
+    <t>wind onshore electricity near Paramagudi (cluster 21)</t>
   </si>
   <si>
     <t>elc_won_IND_022</t>
   </si>
   <si>
-    <t>wind onshore electricity near Agartala (cluster 22)</t>
+    <t>wind onshore electricity near Tinnevelly (cluster 22)</t>
   </si>
   <si>
     <t>elc_won_IND_023</t>
   </si>
   <si>
-    <t>wind onshore electricity near Kolkata (cluster 23)</t>
+    <t>wind onshore electricity near Dhulia (cluster 23)</t>
   </si>
   <si>
     <t>elc_won_IND_024</t>
   </si>
   <si>
-    <t>wind onshore electricity near Bhubaneshwar (cluster 24)</t>
+    <t>wind onshore electricity near Akola (cluster 24)</t>
   </si>
   <si>
     <t>elc_won_IND_025</t>
   </si>
   <si>
-    <t>wind onshore electricity near Bankura (cluster 25)</t>
+    <t>wind onshore electricity near Gondal (cluster 25)</t>
   </si>
   <si>
     <t>elc_won_IND_026</t>
   </si>
   <si>
-    <t>wind onshore electricity near Raneswar (cluster 26)</t>
+    <t>wind onshore electricity near Bardoli (cluster 26)</t>
   </si>
   <si>
     <t>elc_won_IND_027</t>
   </si>
   <si>
-    <t>wind onshore electricity near Supaul (cluster 27)</t>
+    <t>wind onshore electricity near Jaisalmer (cluster 27)</t>
   </si>
   <si>
     <t>elc_won_IND_028</t>
   </si>
   <si>
-    <t>wind onshore electricity near Balurghat (cluster 28)</t>
+    <t>wind onshore electricity near Bikaner (cluster 28)</t>
   </si>
   <si>
     <t>elc_won_IND_029</t>
   </si>
   <si>
-    <t>wind onshore electricity near Peruvancha (cluster 29)</t>
+    <t>wind onshore electricity near Ganganagar (cluster 29)</t>
   </si>
   <si>
     <t>elc_won_IND_030</t>
   </si>
   <si>
-    <t>wind onshore electricity near Ongole (cluster 30)</t>
+    <t>wind onshore electricity near Bikaner (cluster 30)</t>
   </si>
   <si>
     <t>elc_won_IND_031</t>
   </si>
   <si>
-    <t>wind onshore electricity near Kothapet (cluster 31)</t>
+    <t>wind onshore electricity near Shiv (cluster 31)</t>
   </si>
   <si>
     <t>elc_won_IND_032</t>
   </si>
   <si>
-    <t>wind onshore electricity near Jeypore (cluster 32)</t>
+    <t>wind onshore electricity near Bhuj (cluster 32)</t>
   </si>
   <si>
     <t>elc_won_IND_033</t>
   </si>
   <si>
-    <t>wind onshore electricity near Amravati (cluster 33)</t>
+    <t>wind onshore electricity near Rapar (cluster 33)</t>
   </si>
   <si>
     <t>elc_won_IND_034</t>
   </si>
   <si>
-    <t>wind onshore electricity near Sirur (cluster 34)</t>
+    <t>wind onshore electricity near Ahmedabad (cluster 34)</t>
   </si>
   <si>
     <t>elc_won_IND_035</t>
   </si>
   <si>
-    <t>wind onshore electricity near Jalgaon (cluster 35)</t>
+    <t>wind onshore electricity near Ratlam (cluster 35)</t>
   </si>
   <si>
     <t>elc_won_IND_036</t>
   </si>
   <si>
-    <t>wind onshore electricity near Paramagudi (cluster 36)</t>
+    <t>wind onshore electricity near Bhopal (cluster 36)</t>
   </si>
   <si>
     <t>elc_won_IND_037</t>
   </si>
   <si>
-    <t>wind onshore electricity near Oulgaret (cluster 37)</t>
+    <t>wind onshore electricity near Biaora (cluster 37)</t>
   </si>
   <si>
     <t>elc_won_IND_038</t>
   </si>
   <si>
-    <t>wind onshore electricity near Markapur (cluster 38)</t>
+    <t>wind onshore electricity near Bijaynagar (cluster 38)</t>
   </si>
   <si>
     <t>elc_won_IND_039</t>
   </si>
   <si>
-    <t>wind onshore electricity near Tiruvannamalai (cluster 39)</t>
+    <t>wind onshore electricity near Jaipur (cluster 39)</t>
   </si>
   <si>
     <t>elc_won_IND_040</t>
   </si>
   <si>
-    <t>wind onshore electricity near Malkajgiri (cluster 40)</t>
+    <t>wind onshore electricity near Puri (cluster 40)</t>
   </si>
   <si>
     <t>elc_won_IND_041</t>
   </si>
   <si>
-    <t>wind onshore electricity near Solapur (cluster 41)</t>
+    <t>wind onshore electricity near Agartala (cluster 41)</t>
   </si>
   <si>
     <t>elc_won_IND_042</t>
   </si>
   <si>
-    <t>wind onshore electricity near Anantapur (cluster 42)</t>
+    <t>wind onshore electricity near Barddhaman (cluster 42)</t>
   </si>
   <si>
     <t>elc_won_IND_043</t>
   </si>
   <si>
-    <t>wind onshore electricity near Mahad (cluster 43)</t>
+    <t>wind onshore electricity near Uluberiya (cluster 43)</t>
   </si>
   <si>
     <t>elc_won_IND_044</t>
   </si>
   <si>
-    <t>wind onshore electricity near Kolhapur (cluster 44)</t>
+    <t>wind onshore electricity near Ingraj Bazar (cluster 44)</t>
   </si>
   <si>
     <t>elc_won_IND_045</t>
   </si>
   <si>
-    <t>wind onshore electricity near Bodinayakkanur (cluster 45)</t>
+    <t>wind onshore electricity near Dagarua (cluster 45)</t>
   </si>
   <si>
     <t>elc_won_IND_046</t>
   </si>
   <si>
-    <t>wind onshore electricity near Mysore (cluster 46)</t>
+    <t>wind onshore electricity near Deoghar (cluster 46)</t>
   </si>
   <si>
     <t>elc_won_IND_047</t>
   </si>
   <si>
-    <t>wind onshore electricity near Hubli (cluster 47)</t>
+    <t>wind onshore electricity near Ranchi (cluster 47)</t>
   </si>
   <si>
     <t>elc_won_IND_048</t>
   </si>
   <si>
-    <t>wind onshore electricity near Gandhidham (cluster 48)</t>
+    <t>wind onshore electricity near Delhi (cluster 48)</t>
   </si>
   <si>
     <t>elc_won_IND_049</t>
   </si>
   <si>
-    <t>wind onshore electricity near Nasik (cluster 49)</t>
+    <t>wind onshore electricity near Karnal (cluster 49)</t>
   </si>
   <si>
     <t>elc_won_IND_050</t>
   </si>
   <si>
-    <t>wind onshore electricity near Bhavnagar (cluster 50)</t>
+    <t>wind onshore electricity near Moradabad (cluster 50)</t>
   </si>
   <si>
     <t>elc_won_IND_051</t>
   </si>
   <si>
-    <t>wind onshore electricity near Modasa (cluster 51)</t>
+    <t>wind onshore electricity near Etah (cluster 51)</t>
   </si>
   <si>
     <t>elc_won_IND_052</t>
   </si>
   <si>
-    <t>wind onshore electricity near Jodhpur (cluster 52)</t>
+    <t>wind onshore electricity near Sirsa (cluster 52)</t>
   </si>
   <si>
     <t>elc_won_IND_053</t>
   </si>
   <si>
-    <t>wind onshore electricity near Raniwara Kalan (cluster 53)</t>
+    <t>wind onshore electricity near Bharatpur (cluster 53)</t>
   </si>
   <si>
     <t>elc_won_IND_054</t>
   </si>
   <si>
-    <t>wind onshore electricity near Gadarwara (cluster 54)</t>
+    <t>wind onshore electricity near Bhiwani (cluster 54)</t>
   </si>
   <si>
     <t>elc_won_IND_055</t>
   </si>
   <si>
-    <t>wind onshore electricity near Indore (cluster 55)</t>
+    <t>wind onshore electricity near Darbhanga (cluster 55)</t>
   </si>
   <si>
     <t>elc_won_IND_056</t>
   </si>
   <si>
-    <t>wind onshore electricity near Shujalpur (cluster 56)</t>
+    <t>wind onshore electricity near Gorakhpur (cluster 56)</t>
   </si>
   <si>
     <t>elc_won_IND_057</t>
   </si>
   <si>
-    <t>wind onshore electricity near Bijaynagar (cluster 57)</t>
+    <t>wind onshore electricity near Sitapur (cluster 57)</t>
   </si>
   <si>
     <t>elc_won_IND_058</t>
   </si>
   <si>
-    <t>wind onshore electricity near Sawai Madhopur (cluster 58)</t>
+    <t>wind onshore electricity near Sasaram (cluster 58)</t>
   </si>
   <si>
     <t>elc_won_IND_059</t>
   </si>
   <si>
-    <t>wind onshore electricity near Rath (cluster 59)</t>
+    <t>wind onshore electricity near Kanpur (cluster 59)</t>
   </si>
   <si>
     <t>elc_won_IND_060</t>
   </si>
   <si>
-    <t>wind onshore electricity near Jhansi (cluster 60)</t>
+    <t>wind onshore electricity near Prayagraj (cluster 60)</t>
   </si>
   <si>
     <t>elc_won_IND_061</t>
   </si>
   <si>
-    <t>wind onshore electricity near Mansa (cluster 61)</t>
+    <t>wind onshore electricity near Sidhi (cluster 61)</t>
   </si>
   <si>
     <t>elc_won_IND_062</t>
   </si>
   <si>
-    <t>wind onshore electricity near Alwar (cluster 62)</t>
+    <t>wind onshore electricity near Panna (cluster 62)</t>
   </si>
   <si>
     <t>elc_won_IND_063</t>
   </si>
   <si>
-    <t>wind onshore electricity near Hisar (cluster 63)</t>
+    <t>wind onshore electricity near Katri (cluster 63)</t>
   </si>
   <si>
     <t>elc_won_IND_064</t>
   </si>
   <si>
-    <t>wind onshore electricity near Jaisalmer (cluster 64)</t>
+    <t>wind onshore electricity near Orai (cluster 64)</t>
   </si>
   <si>
     <t>elc_won_IND_065</t>
   </si>
   <si>
-    <t>wind onshore electricity near Suratgarh (cluster 65)</t>
+    <t>wind onshore electricity near Gwalior (cluster 65)</t>
   </si>
   <si>
     <t>elc_won_IND_066</t>
   </si>
   <si>
-    <t>wind onshore electricity near Sikar (cluster 66)</t>
-  </si>
-  <si>
-    <t>elc_won_IND_067</t>
-  </si>
-  <si>
-    <t>wind onshore electricity near Nokha (cluster 67)</t>
+    <t>wind onshore electricity near Chhatarpur (cluster 66)</t>
   </si>
   <si>
     <t>~fi_comm</t>
@@ -4398,13 +4392,13 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37AC575F-2E7D-4548-A9CA-D3B4EAC78D00}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3255914-0D34-4AC0-9662-C5256324C788}">
   <dimension ref="B3:I20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="3" spans="2:9">
       <c r="B3" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -4438,13 +4432,13 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="D5" t="s">
         <v>241</v>
       </c>
       <c r="E5" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="F5" t="s">
         <v>233</v>
@@ -4453,7 +4447,7 @@
         <v>232</v>
       </c>
       <c r="H5" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="I5" t="s">
         <v>245</v>
@@ -4464,13 +4458,13 @@
         <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="D6" t="s">
         <v>241</v>
       </c>
       <c r="E6" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="F6" t="s">
         <v>233</v>
@@ -4479,7 +4473,7 @@
         <v>232</v>
       </c>
       <c r="H6" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="I6" t="s">
         <v>245</v>
@@ -4490,13 +4484,13 @@
         <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="D7" t="s">
         <v>241</v>
       </c>
       <c r="E7" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="F7" t="s">
         <v>233</v>
@@ -4505,7 +4499,7 @@
         <v>232</v>
       </c>
       <c r="H7" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="I7" t="s">
         <v>245</v>
@@ -4516,13 +4510,13 @@
         <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="D8" t="s">
         <v>241</v>
       </c>
       <c r="E8" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="F8" t="s">
         <v>233</v>
@@ -4531,7 +4525,7 @@
         <v>232</v>
       </c>
       <c r="H8" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="I8" t="s">
         <v>245</v>
@@ -4542,13 +4536,13 @@
         <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="D9" t="s">
         <v>241</v>
       </c>
       <c r="E9" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="F9" t="s">
         <v>233</v>
@@ -4557,7 +4551,7 @@
         <v>232</v>
       </c>
       <c r="H9" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="I9" t="s">
         <v>245</v>
@@ -4568,13 +4562,13 @@
         <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="D10" t="s">
         <v>241</v>
       </c>
       <c r="E10" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="F10" t="s">
         <v>233</v>
@@ -4583,7 +4577,7 @@
         <v>232</v>
       </c>
       <c r="H10" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="I10" t="s">
         <v>245</v>
@@ -4594,13 +4588,13 @@
         <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="D11" t="s">
         <v>241</v>
       </c>
       <c r="E11" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="F11" t="s">
         <v>233</v>
@@ -4609,7 +4603,7 @@
         <v>232</v>
       </c>
       <c r="H11" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="I11" t="s">
         <v>245</v>
@@ -4620,13 +4614,13 @@
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="D12" t="s">
         <v>241</v>
       </c>
       <c r="E12" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="F12" t="s">
         <v>233</v>
@@ -4635,7 +4629,7 @@
         <v>232</v>
       </c>
       <c r="H12" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="I12" t="s">
         <v>245</v>
@@ -4646,13 +4640,13 @@
         <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="D13" t="s">
         <v>241</v>
       </c>
       <c r="E13" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="F13" t="s">
         <v>233</v>
@@ -4661,7 +4655,7 @@
         <v>232</v>
       </c>
       <c r="H13" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="I13" t="s">
         <v>245</v>
@@ -4672,13 +4666,13 @@
         <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="D14" t="s">
         <v>241</v>
       </c>
       <c r="E14" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="F14" t="s">
         <v>233</v>
@@ -4687,7 +4681,7 @@
         <v>232</v>
       </c>
       <c r="H14" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="I14" t="s">
         <v>245</v>
@@ -4698,13 +4692,13 @@
         <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="D15" t="s">
         <v>241</v>
       </c>
       <c r="E15" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="F15" t="s">
         <v>233</v>
@@ -4713,7 +4707,7 @@
         <v>232</v>
       </c>
       <c r="H15" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="I15" t="s">
         <v>245</v>
@@ -4724,13 +4718,13 @@
         <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="D16" t="s">
         <v>241</v>
       </c>
       <c r="E16" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="F16" t="s">
         <v>233</v>
@@ -4739,7 +4733,7 @@
         <v>232</v>
       </c>
       <c r="H16" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="I16" t="s">
         <v>245</v>
@@ -4750,13 +4744,13 @@
         <v>17</v>
       </c>
       <c r="C17" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="D17" t="s">
         <v>241</v>
       </c>
       <c r="E17" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="F17" t="s">
         <v>233</v>
@@ -4765,7 +4759,7 @@
         <v>232</v>
       </c>
       <c r="H17" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="I17" t="s">
         <v>245</v>
@@ -4776,13 +4770,13 @@
         <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="D18" t="s">
         <v>241</v>
       </c>
       <c r="E18" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="F18" t="s">
         <v>233</v>
@@ -4791,7 +4785,7 @@
         <v>232</v>
       </c>
       <c r="H18" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="I18" t="s">
         <v>245</v>
@@ -4802,13 +4796,13 @@
         <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="D19" t="s">
         <v>241</v>
       </c>
       <c r="E19" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="F19" t="s">
         <v>233</v>
@@ -4817,7 +4811,7 @@
         <v>232</v>
       </c>
       <c r="H19" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="I19" t="s">
         <v>245</v>
@@ -4828,13 +4822,13 @@
         <v>17</v>
       </c>
       <c r="C20" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="D20" t="s">
         <v>241</v>
       </c>
       <c r="E20" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="F20" t="s">
         <v>233</v>
@@ -4843,7 +4837,7 @@
         <v>232</v>
       </c>
       <c r="H20" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="I20" t="s">
         <v>245</v>
@@ -4855,13 +4849,13 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF70EA25-F084-476B-8575-FF9CBC45EB17}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F048C95-4FDA-41C6-88CC-90067C04E5C4}">
   <dimension ref="B3:I20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="3" spans="2:9">
       <c r="B3" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -4895,22 +4889,22 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
+        <v>581</v>
+      </c>
+      <c r="D5" t="s">
+        <v>241</v>
+      </c>
+      <c r="E5" t="s">
+        <v>582</v>
+      </c>
+      <c r="F5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" t="s">
         <v>583</v>
-      </c>
-      <c r="D5" t="s">
-        <v>241</v>
-      </c>
-      <c r="E5" t="s">
-        <v>584</v>
-      </c>
-      <c r="F5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G5" t="s">
-        <v>35</v>
-      </c>
-      <c r="H5" t="s">
-        <v>585</v>
       </c>
       <c r="I5" t="s">
         <v>245</v>
@@ -4921,13 +4915,13 @@
         <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="D6" t="s">
         <v>241</v>
       </c>
       <c r="E6" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="F6" t="s">
         <v>25</v>
@@ -4936,7 +4930,7 @@
         <v>35</v>
       </c>
       <c r="H6" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="I6" t="s">
         <v>245</v>
@@ -4947,13 +4941,13 @@
         <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="D7" t="s">
         <v>241</v>
       </c>
       <c r="E7" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="F7" t="s">
         <v>25</v>
@@ -4962,7 +4956,7 @@
         <v>35</v>
       </c>
       <c r="H7" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="I7" t="s">
         <v>245</v>
@@ -4973,13 +4967,13 @@
         <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="D8" t="s">
         <v>241</v>
       </c>
       <c r="E8" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="F8" t="s">
         <v>25</v>
@@ -4988,7 +4982,7 @@
         <v>35</v>
       </c>
       <c r="H8" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="I8" t="s">
         <v>245</v>
@@ -4999,13 +4993,13 @@
         <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="D9" t="s">
         <v>241</v>
       </c>
       <c r="E9" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="F9" t="s">
         <v>25</v>
@@ -5014,7 +5008,7 @@
         <v>35</v>
       </c>
       <c r="H9" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="I9" t="s">
         <v>245</v>
@@ -5025,13 +5019,13 @@
         <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="D10" t="s">
         <v>241</v>
       </c>
       <c r="E10" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="F10" t="s">
         <v>25</v>
@@ -5040,7 +5034,7 @@
         <v>35</v>
       </c>
       <c r="H10" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="I10" t="s">
         <v>245</v>
@@ -5051,13 +5045,13 @@
         <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="D11" t="s">
         <v>241</v>
       </c>
       <c r="E11" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="F11" t="s">
         <v>25</v>
@@ -5066,7 +5060,7 @@
         <v>35</v>
       </c>
       <c r="H11" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="I11" t="s">
         <v>245</v>
@@ -5077,13 +5071,13 @@
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="D12" t="s">
         <v>241</v>
       </c>
       <c r="E12" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="F12" t="s">
         <v>25</v>
@@ -5092,7 +5086,7 @@
         <v>35</v>
       </c>
       <c r="H12" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="I12" t="s">
         <v>245</v>
@@ -5103,13 +5097,13 @@
         <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="D13" t="s">
         <v>241</v>
       </c>
       <c r="E13" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F13" t="s">
         <v>25</v>
@@ -5118,7 +5112,7 @@
         <v>35</v>
       </c>
       <c r="H13" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="I13" t="s">
         <v>245</v>
@@ -5129,13 +5123,13 @@
         <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="D14" t="s">
         <v>241</v>
       </c>
       <c r="E14" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="F14" t="s">
         <v>25</v>
@@ -5144,7 +5138,7 @@
         <v>35</v>
       </c>
       <c r="H14" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="I14" t="s">
         <v>245</v>
@@ -5155,13 +5149,13 @@
         <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="D15" t="s">
         <v>241</v>
       </c>
       <c r="E15" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="F15" t="s">
         <v>25</v>
@@ -5170,7 +5164,7 @@
         <v>35</v>
       </c>
       <c r="H15" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="I15" t="s">
         <v>245</v>
@@ -5181,13 +5175,13 @@
         <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="D16" t="s">
         <v>241</v>
       </c>
       <c r="E16" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="F16" t="s">
         <v>25</v>
@@ -5196,7 +5190,7 @@
         <v>35</v>
       </c>
       <c r="H16" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="I16" t="s">
         <v>245</v>
@@ -5207,13 +5201,13 @@
         <v>17</v>
       </c>
       <c r="C17" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="D17" t="s">
         <v>241</v>
       </c>
       <c r="E17" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="F17" t="s">
         <v>25</v>
@@ -5222,7 +5216,7 @@
         <v>35</v>
       </c>
       <c r="H17" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="I17" t="s">
         <v>245</v>
@@ -5233,13 +5227,13 @@
         <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="D18" t="s">
         <v>241</v>
       </c>
       <c r="E18" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="F18" t="s">
         <v>25</v>
@@ -5248,7 +5242,7 @@
         <v>35</v>
       </c>
       <c r="H18" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="I18" t="s">
         <v>245</v>
@@ -5259,13 +5253,13 @@
         <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="D19" t="s">
         <v>241</v>
       </c>
       <c r="E19" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="F19" t="s">
         <v>25</v>
@@ -5274,7 +5268,7 @@
         <v>35</v>
       </c>
       <c r="H19" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="I19" t="s">
         <v>245</v>
@@ -5285,13 +5279,13 @@
         <v>17</v>
       </c>
       <c r="C20" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="D20" t="s">
         <v>241</v>
       </c>
       <c r="E20" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="F20" t="s">
         <v>25</v>
@@ -5300,7 +5294,7 @@
         <v>35</v>
       </c>
       <c r="H20" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="I20" t="s">
         <v>245</v>
@@ -5313,7 +5307,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2F298A9-BCD9-4ABF-BE3B-9D1BDD3E7001}">
-  <dimension ref="B3:S173"/>
+  <dimension ref="B3:S172"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="11.140625" bestFit="1" customWidth="1"/>
@@ -9623,29 +9617,6 @@
         <v>35</v>
       </c>
       <c r="S172" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="173" spans="13:19">
-      <c r="M173" t="s">
-        <v>17</v>
-      </c>
-      <c r="N173" t="s">
-        <v>580</v>
-      </c>
-      <c r="O173" t="s">
-        <v>241</v>
-      </c>
-      <c r="P173" t="s">
-        <v>581</v>
-      </c>
-      <c r="Q173" t="s">
-        <v>25</v>
-      </c>
-      <c r="R173" t="s">
-        <v>35</v>
-      </c>
-      <c r="S173" t="s">
         <v>245</v>
       </c>
     </row>
